--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2344,12 +2464,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3708-258-CM25</t>
+          <t>5056-960-SE25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2364,48 +2484,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17802.4</v>
+        <v>688920.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3621-135-CM25</t>
+          <t>3708-258-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,53 +2544,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>16512.92</v>
+        <v>17802.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2790-158-CM25</t>
+          <t>3621-135-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,43 +2619,47 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>17068.17</v>
+        <v>16512.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>542429-13-CM25</t>
+          <t>2790-158-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2699,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2714,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8508.02</v>
+        <v>17068.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4454-395-CM25</t>
+          <t>542429-13-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,48 +2740,52 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2309.08</v>
+        <v>8508.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>188-312-CM25</t>
+          <t>4454-395-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2800,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,43 +2810,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>16429.35</v>
+        <v>2309.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2403-299-CM25</t>
+          <t>188-312-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2875,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2758,20 +2898,24 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1174.58</v>
+        <v>16429.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2387-226-CM25</t>
+          <t>2403-299-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2930,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,43 +2940,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8779.76</v>
+        <v>1174.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>752-174-CM25</t>
+          <t>2387-226-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,53 +2995,57 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10575.53</v>
+        <v>8779.76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>483-223-CM25</t>
+          <t>752-174-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,43 +3070,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.607.103-3</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION ARAUCO HOSPITAL DE CONTULMO</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3998.4</v>
+        <v>10575.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4455-217-CM25</t>
+          <t>483-223-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +3135,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.103-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO DE SALUD CONCEPCION ARAUCO HOSPITAL DE CONTULMO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3150,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3165,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11135.31</v>
+        <v>3998.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3108-34-CM25</t>
+          <t>4455-217-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,43 +3196,47 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.926.100-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>BOOKCOMPUTER</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1812.93</v>
+        <v>11135.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4455-220-CM25</t>
+          <t>3108-34-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,43 +3261,47 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.926.100-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2141.41</v>
+        <v>1812.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3705-173-CM25</t>
+          <t>4455-220-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,48 +3321,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12333.06</v>
+        <v>2141.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4856-186-CM25</t>
+          <t>3705-173-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,48 +3386,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2249.1</v>
+        <v>12333.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3712-398-CM25</t>
+          <t>4856-186-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3446,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,27 +3456,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,67 +3486,136 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5872.89</v>
+        <v>2249.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>3712-398-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>5872.89</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>1057439-13532-CM25</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>abr-2025</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>61.606.402-9</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Coquimbo</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>46532.33</v>
       </c>
     </row>
